--- a/research/traditional_assets/database/data/burkina_faso/burkina_faso_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/burkina_faso/burkina_faso_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.273</v>
+        <v>0.006000000000000019</v>
       </c>
       <c r="E2">
-        <v>0.117</v>
+        <v>0.169</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,10 +606,10 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>38.2</v>
+        <v>115.5</v>
       </c>
       <c r="L2">
-        <v>0.4817150063051703</v>
+        <v>0.5160857908847185</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -639,25 +639,25 @@
         <v>0</v>
       </c>
       <c r="W2">
-        <v>0.2802641232575201</v>
+        <v>0.2483870374204658</v>
       </c>
       <c r="X2">
-        <v>0.07090198047114164</v>
+        <v>0.1223889701408341</v>
       </c>
       <c r="Y2">
-        <v>0.2093621427863785</v>
+        <v>0.1259980672796318</v>
       </c>
       <c r="Z2">
-        <v>0.5818048422597212</v>
+        <v>0.5005591590248266</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07090198047114164</v>
+        <v>0.1223889701408341</v>
       </c>
       <c r="AC2">
-        <v>-0.07090198047114164</v>
+        <v>-0.1223889701408341</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -698,7 +698,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bank of Africa-Burkina Faso (BRVM:BOABF)</t>
+          <t>Coris Bank International SA (BRVM:CBIBF)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -707,10 +707,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.273</v>
+        <v>0.231</v>
       </c>
       <c r="E3">
-        <v>0.117</v>
+        <v>0.222</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -725,10 +725,10 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>38.2</v>
+        <v>82.2</v>
       </c>
       <c r="L3">
-        <v>0.4817150063051703</v>
+        <v>0.5502008032128514</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,25 +758,25 @@
         <v>0</v>
       </c>
       <c r="W3">
-        <v>0.2802641232575201</v>
+        <v>0.2802591203545857</v>
       </c>
       <c r="X3">
-        <v>0.07090198047114164</v>
+        <v>0.1223889701408341</v>
       </c>
       <c r="Y3">
-        <v>0.2093621427863785</v>
+        <v>0.1578701502137517</v>
       </c>
       <c r="Z3">
-        <v>0.5818048422597212</v>
+        <v>0.5093760654619843</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.07090198047114164</v>
+        <v>0.1223889701408341</v>
       </c>
       <c r="AC3">
-        <v>-0.07090198047114164</v>
+        <v>-0.1223889701408341</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -806,6 +806,125 @@
         <v>0</v>
       </c>
       <c r="AM3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Burkina Faso</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Bank of Africa - Burkina Faso (BRVM:BOABF)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>-0.219</v>
+      </c>
+      <c r="E4">
+        <v>0.116</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>33.3</v>
+      </c>
+      <c r="L4">
+        <v>0.4475806451612903</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>-0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>-0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0.2165149544863459</v>
+      </c>
+      <c r="X4">
+        <v>0.1223889701408341</v>
+      </c>
+      <c r="Y4">
+        <v>0.0941259843455118</v>
+      </c>
+      <c r="Z4">
+        <v>0.4837451235370611</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0.1223889701408341</v>
+      </c>
+      <c r="AC4">
+        <v>-0.1223889701408341</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/burkina_faso/burkina_faso_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/burkina_faso/burkina_faso_bank_money_center.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.006000000000000019</v>
+        <v>0.168</v>
       </c>
       <c r="E2">
-        <v>0.169</v>
+        <v>0.1815</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,10 +606,10 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>115.5</v>
+        <v>146.8</v>
       </c>
       <c r="L2">
-        <v>0.5160857908847185</v>
+        <v>0.5500187336080931</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -639,25 +639,25 @@
         <v>0</v>
       </c>
       <c r="W2">
-        <v>0.2483870374204658</v>
+        <v>0.3282464058495507</v>
       </c>
       <c r="X2">
-        <v>0.1223889701408341</v>
+        <v>0.1000766334477969</v>
       </c>
       <c r="Y2">
-        <v>0.1259980672796318</v>
+        <v>0.2281697724017537</v>
       </c>
       <c r="Z2">
-        <v>0.5005591590248266</v>
+        <v>0.602619101377286</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.1223889701408341</v>
+        <v>0.1000766334477969</v>
       </c>
       <c r="AC2">
-        <v>-0.1223889701408341</v>
+        <v>-0.1000766334477969</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -698,7 +698,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Coris Bank International SA (BRVM:CBIBF)</t>
+          <t>Bank of Africa - Burkina Faso (BRVM:BOABF)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -706,11 +706,8 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.231</v>
-      </c>
       <c r="E3">
-        <v>0.222</v>
+        <v>0.131</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -725,10 +722,10 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>82.2</v>
+        <v>46.4</v>
       </c>
       <c r="L3">
-        <v>0.5502008032128514</v>
+        <v>0.4989247311827957</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,25 +755,25 @@
         <v>0</v>
       </c>
       <c r="W3">
-        <v>0.2802591203545857</v>
+        <v>0.3189003436426117</v>
       </c>
       <c r="X3">
-        <v>0.1223889701408341</v>
+        <v>0.1000766334477969</v>
       </c>
       <c r="Y3">
-        <v>0.1578701502137517</v>
+        <v>0.2188237101948147</v>
       </c>
       <c r="Z3">
-        <v>0.5093760654619843</v>
+        <v>0.6391752577319587</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.1223889701408341</v>
+        <v>0.1000766334477969</v>
       </c>
       <c r="AC3">
-        <v>-0.1223889701408341</v>
+        <v>-0.1000766334477969</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -817,7 +814,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bank of Africa - Burkina Faso (BRVM:BOABF)</t>
+          <t>Coris Bank International SA (BRVM:CBIBF)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -826,10 +823,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.219</v>
+        <v>0.168</v>
       </c>
       <c r="E4">
-        <v>0.116</v>
+        <v>0.232</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -844,10 +841,10 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>33.3</v>
+        <v>100.4</v>
       </c>
       <c r="L4">
-        <v>0.4475806451612903</v>
+        <v>0.5773433007475561</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -877,25 +874,25 @@
         <v>0</v>
       </c>
       <c r="W4">
-        <v>0.2165149544863459</v>
+        <v>0.3375924680564896</v>
       </c>
       <c r="X4">
-        <v>0.1223889701408341</v>
+        <v>0.1000766334477969</v>
       </c>
       <c r="Y4">
-        <v>0.0941259843455118</v>
+        <v>0.2375158346086927</v>
       </c>
       <c r="Z4">
-        <v>0.4837451235370611</v>
+        <v>0.5847343644922663</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.1223889701408341</v>
+        <v>0.1000766334477969</v>
       </c>
       <c r="AC4">
-        <v>-0.1223889701408341</v>
+        <v>-0.1000766334477969</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -912,13 +909,7 @@
       <c r="AH4">
         <v>0</v>
       </c>
-      <c r="AI4">
-        <v>0</v>
-      </c>
       <c r="AJ4">
-        <v>0</v>
-      </c>
-      <c r="AK4">
         <v>0</v>
       </c>
       <c r="AL4">
